--- a/Sindhi Muslim/Staff Record/SMB Staff Record/Staff Record.xlsx
+++ b/Sindhi Muslim/Staff Record/SMB Staff Record/Staff Record.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Staff Record\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Staff Record\SMB Staff Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0229B684-F806-4E96-9B82-81A9B4292286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E58527-5098-4CD9-B0D9-259E76CD6C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -965,6 +965,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -976,6 +977,105 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -986,15 +1086,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1007,97 +1098,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1475,11 +1475,11 @@
   <sheetData>
     <row r="2" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
       <c r="D3" s="53" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Tue</v>
@@ -1604,13 +1604,13 @@
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AI3" s="61" t="s">
+      <c r="AI3" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="61"/>
-      <c r="AK3" s="61"/>
-      <c r="AL3" s="61"/>
-      <c r="AM3" s="62"/>
+      <c r="AJ3" s="62"/>
+      <c r="AK3" s="62"/>
+      <c r="AL3" s="62"/>
+      <c r="AM3" s="63"/>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -2788,11 +2788,11 @@
     </row>
     <row r="16" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A17" s="59" t="s">
+      <c r="A17" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="53" t="str">
         <f>TEXT(D18,"ddd")</f>
         <v>Tue</v>
@@ -2917,13 +2917,13 @@
         <f t="shared" si="7"/>
         <v>Thu</v>
       </c>
-      <c r="AI17" s="61" t="s">
+      <c r="AI17" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="AJ17" s="61"/>
-      <c r="AK17" s="61"/>
-      <c r="AL17" s="61"/>
-      <c r="AM17" s="62"/>
+      <c r="AJ17" s="62"/>
+      <c r="AK17" s="62"/>
+      <c r="AL17" s="62"/>
+      <c r="AM17" s="63"/>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -3926,59 +3926,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="64" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="99"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="66"/>
     </row>
     <row r="2" spans="1:18" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100" t="s">
+      <c r="A2" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="102"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="69"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="70" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="75"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="72"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19"/>
@@ -3997,82 +3997,82 @@
       <c r="N5" s="19"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="79" t="s">
+      <c r="B6" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="79" t="s">
+      <c r="C6" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="82" t="s">
+      <c r="E6" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="82" t="s">
+      <c r="F6" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="82" t="s">
+      <c r="G6" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="82" t="s">
+      <c r="H6" s="79" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="89" t="s">
+      <c r="I6" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="89"/>
-      <c r="K6" s="89"/>
-      <c r="L6" s="89"/>
-      <c r="M6" s="90" t="s">
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="82"/>
+      <c r="M6" s="83" t="s">
         <v>76</v>
       </c>
-      <c r="N6" s="66" t="s">
+      <c r="N6" s="86" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="77"/>
-      <c r="B7" s="80"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="93" t="s">
+      <c r="A7" s="74"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="93" t="s">
+      <c r="J7" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="93" t="s">
+      <c r="K7" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="L7" s="95" t="s">
+      <c r="L7" s="91" t="s">
         <v>41</v>
       </c>
-      <c r="M7" s="91"/>
-      <c r="N7" s="67"/>
+      <c r="M7" s="84"/>
+      <c r="N7" s="87"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="78"/>
-      <c r="B8" s="81"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="81"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="94"/>
-      <c r="J8" s="94"/>
-      <c r="K8" s="94"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="92"/>
-      <c r="N8" s="68"/>
+      <c r="A8" s="75"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="90"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="90"/>
+      <c r="L8" s="92"/>
+      <c r="M8" s="85"/>
+      <c r="N8" s="88"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
@@ -4122,10 +4122,10 @@
       <c r="O9" t="s">
         <v>101</v>
       </c>
-      <c r="P9" s="103">
+      <c r="P9" s="59">
         <v>43313</v>
       </c>
-      <c r="Q9" s="103">
+      <c r="Q9" s="59">
         <v>44682</v>
       </c>
       <c r="R9">
@@ -4527,22 +4527,22 @@
       <c r="N19" s="19"/>
     </row>
     <row r="20" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="73" t="s">
+      <c r="A20" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="74"/>
-      <c r="C20" s="74"/>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="74"/>
-      <c r="J20" s="74"/>
-      <c r="K20" s="74"/>
-      <c r="L20" s="74"/>
-      <c r="M20" s="74"/>
-      <c r="N20" s="75"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="71"/>
+      <c r="L20" s="71"/>
+      <c r="M20" s="71"/>
+      <c r="N20" s="72"/>
     </row>
     <row r="21" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19"/>
@@ -4561,82 +4561,82 @@
       <c r="N21" s="19"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="76" t="s">
+      <c r="A22" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="79" t="s">
+      <c r="B22" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="79" t="s">
+      <c r="C22" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="79" t="s">
+      <c r="D22" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="82" t="s">
+      <c r="E22" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="82" t="s">
+      <c r="F22" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="G22" s="85" t="s">
+      <c r="G22" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="H22" s="85" t="s">
+      <c r="H22" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="I22" s="88" t="s">
+      <c r="I22" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="J22" s="88"/>
-      <c r="K22" s="88"/>
-      <c r="L22" s="88"/>
-      <c r="M22" s="63" t="s">
+      <c r="J22" s="96"/>
+      <c r="K22" s="96"/>
+      <c r="L22" s="96"/>
+      <c r="M22" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="N22" s="66" t="s">
+      <c r="N22" s="86" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="77"/>
-      <c r="B23" s="80"/>
-      <c r="C23" s="80"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="80"/>
-      <c r="G23" s="86"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="69" t="s">
+      <c r="A23" s="74"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="94"/>
+      <c r="H23" s="94"/>
+      <c r="I23" s="100" t="s">
         <v>38</v>
       </c>
-      <c r="J23" s="69" t="s">
+      <c r="J23" s="100" t="s">
         <v>39</v>
       </c>
-      <c r="K23" s="69" t="s">
+      <c r="K23" s="100" t="s">
         <v>40</v>
       </c>
-      <c r="L23" s="71" t="s">
+      <c r="L23" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="M23" s="64"/>
-      <c r="N23" s="67"/>
+      <c r="M23" s="98"/>
+      <c r="N23" s="87"/>
     </row>
     <row r="24" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="78"/>
-      <c r="B24" s="81"/>
-      <c r="C24" s="81"/>
-      <c r="D24" s="81"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="81"/>
-      <c r="G24" s="87"/>
-      <c r="H24" s="87"/>
-      <c r="I24" s="70"/>
-      <c r="J24" s="70"/>
-      <c r="K24" s="70"/>
-      <c r="L24" s="72"/>
-      <c r="M24" s="65"/>
-      <c r="N24" s="68"/>
+      <c r="A24" s="75"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="78"/>
+      <c r="D24" s="78"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="78"/>
+      <c r="G24" s="95"/>
+      <c r="H24" s="95"/>
+      <c r="I24" s="101"/>
+      <c r="J24" s="101"/>
+      <c r="K24" s="101"/>
+      <c r="L24" s="103"/>
+      <c r="M24" s="99"/>
+      <c r="N24" s="88"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
@@ -4960,6 +4960,24 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A20:N20"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="M22:M24"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="J23:J24"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A4:N4"/>
@@ -4976,37 +4994,19 @@
     <mergeCell ref="N6:N8"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="A20:N20"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="M22:M24"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="L23:L24"/>
   </mergeCells>
-  <conditionalFormatting sqref="B9:M9 B10:C13 M10:M16 D10:L17 C14:C16 F25:F31 G26:I30 D26:E31 K26:M31 G31:J31">
-    <cfRule type="expression" dxfId="2" priority="3">
+  <conditionalFormatting sqref="B25:B30">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>$C25=#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9:M9 B10:C13 M10:M16 D10:L17 C14:C16">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>$C9=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C25:C31">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>$C25=#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D25:E25 G25:M25 B25:B30 J26:J30">
-    <cfRule type="expression" dxfId="0" priority="2">
+  <conditionalFormatting sqref="C25:M31">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$C25=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
